--- a/data/saint macro su nombre original es (Inventario_Fisico) sin parentesis.xlsx
+++ b/data/saint macro su nombre original es (Inventario_Fisico) sin parentesis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\licores\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281057E9-5268-4D46-82E9-056D96AE71E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E562147F-10E0-4ABD-87A7-446D5435DBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
